--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123304265</v>
+        <v>123304264</v>
       </c>
       <c r="B2" t="n">
-        <v>91243</v>
+        <v>90966</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598319</v>
+        <v>598355</v>
       </c>
       <c r="R2" t="n">
-        <v>6922248</v>
+        <v>6922329</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123304257</v>
+        <v>123304259</v>
       </c>
       <c r="B3" t="n">
-        <v>90963</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,47 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598358</v>
+        <v>598360</v>
       </c>
       <c r="R3" t="n">
-        <v>6922402</v>
+        <v>6922325</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +866,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -885,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123304264</v>
+        <v>123304268</v>
       </c>
       <c r="B4" t="n">
-        <v>90963</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,38 +929,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598355</v>
+        <v>598312</v>
       </c>
       <c r="R4" t="n">
-        <v>6922329</v>
+        <v>6922247</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1006,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1031,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Erik Lagerin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1047,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123304259</v>
+        <v>123304257</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>90966</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,38 +1054,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598360</v>
+        <v>598358</v>
       </c>
       <c r="R5" t="n">
-        <v>6922325</v>
+        <v>6922402</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1121,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1127,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123304268</v>
+        <v>123304265</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>91242</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,38 +1188,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598312</v>
+        <v>598319</v>
       </c>
       <c r="R6" t="n">
-        <v>6922247</v>
+        <v>6922248</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Erik Lagerin</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123304264</v>
+        <v>123304257</v>
       </c>
       <c r="B2" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,17 +708,26 @@
           <t>Niemelä</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598355</v>
+        <v>598358</v>
       </c>
       <c r="R2" t="n">
-        <v>6922329</v>
+        <v>6922402</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1042,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123304257</v>
+        <v>123304265</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>91244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,47 +1063,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598358</v>
+        <v>598319</v>
       </c>
       <c r="R5" t="n">
-        <v>6922402</v>
+        <v>6922248</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1172,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123304265</v>
+        <v>123304264</v>
       </c>
       <c r="B6" t="n">
-        <v>91242</v>
+        <v>90968</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,25 +1184,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598319</v>
+        <v>598355</v>
       </c>
       <c r="R6" t="n">
-        <v>6922248</v>
+        <v>6922329</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123304257</v>
+        <v>123304265</v>
       </c>
       <c r="B2" t="n">
-        <v>90968</v>
+        <v>91250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598358</v>
+        <v>598319</v>
       </c>
       <c r="R2" t="n">
-        <v>6922402</v>
+        <v>6922248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123304259</v>
+        <v>123304257</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>90974</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,38 +808,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598360</v>
+        <v>598358</v>
       </c>
       <c r="R3" t="n">
-        <v>6922325</v>
+        <v>6922402</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123304268</v>
+        <v>123304259</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,38 +942,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598312</v>
+        <v>598360</v>
       </c>
       <c r="R4" t="n">
-        <v>6922247</v>
+        <v>6922325</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +996,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1010,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1036,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Erik Lagerin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1051,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123304265</v>
+        <v>123304264</v>
       </c>
       <c r="B5" t="n">
-        <v>91244</v>
+        <v>90974</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,25 +1059,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598319</v>
+        <v>598355</v>
       </c>
       <c r="R5" t="n">
-        <v>6922248</v>
+        <v>6922329</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1117,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1131,7 +1127,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1137,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123304264</v>
+        <v>123304268</v>
       </c>
       <c r="B6" t="n">
-        <v>90968</v>
+        <v>57634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,38 +1180,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598355</v>
+        <v>598312</v>
       </c>
       <c r="R6" t="n">
-        <v>6922329</v>
+        <v>6922247</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Erik Lagerin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123304265</v>
+        <v>123304264</v>
       </c>
       <c r="B2" t="n">
-        <v>91250</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598319</v>
+        <v>598355</v>
       </c>
       <c r="R2" t="n">
-        <v>6922248</v>
+        <v>6922329</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Erik Lagerin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123304257</v>
+        <v>123304268</v>
       </c>
       <c r="B3" t="n">
-        <v>90974</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,35 +808,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598358</v>
+        <v>598312</v>
       </c>
       <c r="R3" t="n">
-        <v>6922402</v>
+        <v>6922247</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +870,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -885,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +910,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -926,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123304259</v>
+        <v>123304257</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,38 +933,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598360</v>
+        <v>598358</v>
       </c>
       <c r="R4" t="n">
-        <v>6922325</v>
+        <v>6922402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +1000,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1006,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123304264</v>
+        <v>123304259</v>
       </c>
       <c r="B5" t="n">
-        <v>90974</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1063,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598355</v>
+        <v>598360</v>
       </c>
       <c r="R5" t="n">
-        <v>6922329</v>
+        <v>6922325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1121,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1127,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1161,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1168,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123304268</v>
+        <v>123304265</v>
       </c>
       <c r="B6" t="n">
-        <v>57634</v>
+        <v>91253</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,38 +1188,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598312</v>
+        <v>598319</v>
       </c>
       <c r="R6" t="n">
-        <v>6922247</v>
+        <v>6922248</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">

--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123304264</v>
+        <v>123304268</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>57640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598355</v>
+        <v>598312</v>
       </c>
       <c r="R2" t="n">
-        <v>6922329</v>
+        <v>6922247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123304268</v>
+        <v>123304259</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,38 +816,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598312</v>
+        <v>598360</v>
       </c>
       <c r="R3" t="n">
-        <v>6922247</v>
+        <v>6922325</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123304257</v>
+        <v>123304264</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>90994</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,26 +954,17 @@
           <t>Niemelä</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598358</v>
+        <v>598355</v>
       </c>
       <c r="R4" t="n">
-        <v>6922402</v>
+        <v>6922329</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +991,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1010,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1031,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1051,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123304259</v>
+        <v>123304257</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>90994</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,38 +1054,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598360</v>
+        <v>598358</v>
       </c>
       <c r="R5" t="n">
-        <v>6922325</v>
+        <v>6922402</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
         <v>123304265</v>
       </c>
       <c r="B6" t="n">
-        <v>91253</v>
+        <v>91270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Erik Lagerin</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123304268</v>
+        <v>123304257</v>
       </c>
       <c r="B2" t="n">
-        <v>57640</v>
+        <v>90999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598312</v>
+        <v>598358</v>
       </c>
       <c r="R2" t="n">
-        <v>6922247</v>
+        <v>6922402</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Erik Lagerin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123304259</v>
+        <v>123304265</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>91275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598360</v>
+        <v>598319</v>
       </c>
       <c r="R3" t="n">
-        <v>6922325</v>
+        <v>6922248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +875,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -880,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -921,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123304264</v>
+        <v>123304259</v>
       </c>
       <c r="B4" t="n">
-        <v>90994</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,25 +938,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -961,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598355</v>
+        <v>598360</v>
       </c>
       <c r="R4" t="n">
-        <v>6922329</v>
+        <v>6922325</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +996,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1001,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1036,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1042,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123304257</v>
+        <v>123304264</v>
       </c>
       <c r="B5" t="n">
-        <v>90994</v>
+        <v>90999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,26 +1080,17 @@
           <t>Niemelä</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598358</v>
+        <v>598355</v>
       </c>
       <c r="R5" t="n">
-        <v>6922402</v>
+        <v>6922329</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1117,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1131,7 +1127,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1137,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1157,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1172,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123304265</v>
+        <v>123304268</v>
       </c>
       <c r="B6" t="n">
-        <v>91270</v>
+        <v>57643</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,34 +1184,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598319</v>
+        <v>598312</v>
       </c>
       <c r="R6" t="n">
-        <v>6922248</v>
+        <v>6922247</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Erik Lagerin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123304257</v>
+        <v>123304268</v>
       </c>
       <c r="B2" t="n">
-        <v>90999</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598358</v>
+        <v>598312</v>
       </c>
       <c r="R2" t="n">
-        <v>6922402</v>
+        <v>6922247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Erik Lagerin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123304265</v>
+        <v>123304264</v>
       </c>
       <c r="B3" t="n">
-        <v>91275</v>
+        <v>91001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598319</v>
+        <v>598355</v>
       </c>
       <c r="R3" t="n">
-        <v>6922248</v>
+        <v>6922329</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +870,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -885,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123304259</v>
+        <v>123304257</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>91001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,38 +933,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598360</v>
+        <v>598358</v>
       </c>
       <c r="R4" t="n">
-        <v>6922325</v>
+        <v>6922402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +1000,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1006,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123304264</v>
+        <v>123304259</v>
       </c>
       <c r="B5" t="n">
-        <v>90999</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1063,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598355</v>
+        <v>598360</v>
       </c>
       <c r="R5" t="n">
-        <v>6922329</v>
+        <v>6922325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1121,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1127,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1161,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1168,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123304268</v>
+        <v>123304265</v>
       </c>
       <c r="B6" t="n">
-        <v>57643</v>
+        <v>91277</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,38 +1188,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598312</v>
+        <v>598319</v>
       </c>
       <c r="R6" t="n">
-        <v>6922247</v>
+        <v>6922248</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Erik Lagerin</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123304268</v>
+        <v>123304257</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
+        <v>91001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598312</v>
+        <v>598358</v>
       </c>
       <c r="R2" t="n">
-        <v>6922247</v>
+        <v>6922402</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Erik Lagerin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123304264</v>
+        <v>123304265</v>
       </c>
       <c r="B3" t="n">
-        <v>91001</v>
+        <v>91277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598355</v>
+        <v>598319</v>
       </c>
       <c r="R3" t="n">
-        <v>6922329</v>
+        <v>6922248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +875,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -880,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +926,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123304257</v>
+        <v>123304264</v>
       </c>
       <c r="B4" t="n">
         <v>91001</v>
@@ -954,26 +959,17 @@
           <t>Niemelä</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598358</v>
+        <v>598355</v>
       </c>
       <c r="R4" t="n">
-        <v>6922402</v>
+        <v>6922329</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +996,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1010,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1036,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1051,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123304259</v>
+        <v>123304268</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,34 +1063,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598360</v>
+        <v>598312</v>
       </c>
       <c r="R5" t="n">
-        <v>6922325</v>
+        <v>6922247</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Erik Lagerin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1172,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123304265</v>
+        <v>123304259</v>
       </c>
       <c r="B6" t="n">
-        <v>91277</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,21 +1188,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598319</v>
+        <v>598360</v>
       </c>
       <c r="R6" t="n">
-        <v>6922248</v>
+        <v>6922325</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123304264</v>
+        <v>123304268</v>
       </c>
       <c r="B4" t="n">
-        <v>91001</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,38 +938,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598355</v>
+        <v>598312</v>
       </c>
       <c r="R4" t="n">
-        <v>6922329</v>
+        <v>6922247</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +1000,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1006,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1040,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Erik Lagerin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1047,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123304268</v>
+        <v>123304264</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>91001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,42 +1063,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598312</v>
+        <v>598355</v>
       </c>
       <c r="R5" t="n">
-        <v>6922247</v>
+        <v>6922329</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Erik Lagerin</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123304257</v>
+        <v>123304265</v>
       </c>
       <c r="B2" t="n">
-        <v>91001</v>
+        <v>91277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598358</v>
+        <v>598319</v>
       </c>
       <c r="R2" t="n">
-        <v>6922402</v>
+        <v>6922248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123304265</v>
+        <v>123304259</v>
       </c>
       <c r="B3" t="n">
-        <v>91277</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598319</v>
+        <v>598360</v>
       </c>
       <c r="R3" t="n">
-        <v>6922248</v>
+        <v>6922325</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +866,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -885,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +906,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -926,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123304268</v>
+        <v>123304257</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>91001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,30 +929,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -970,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598312</v>
+        <v>598358</v>
       </c>
       <c r="R4" t="n">
-        <v>6922247</v>
+        <v>6922402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +996,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1010,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1036,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Erik Lagerin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1172,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123304259</v>
+        <v>123304268</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,34 +1184,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598360</v>
+        <v>598312</v>
       </c>
       <c r="R6" t="n">
-        <v>6922325</v>
+        <v>6922247</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Erik Lagerin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123304259</v>
+        <v>123304257</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>91001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +808,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598360</v>
+        <v>598358</v>
       </c>
       <c r="R3" t="n">
-        <v>6922325</v>
+        <v>6922402</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +875,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -876,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +926,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123304257</v>
+        <v>123304264</v>
       </c>
       <c r="B4" t="n">
         <v>91001</v>
@@ -950,26 +959,17 @@
           <t>Niemelä</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598358</v>
+        <v>598355</v>
       </c>
       <c r="R4" t="n">
-        <v>6922402</v>
+        <v>6922329</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123304264</v>
+        <v>123304268</v>
       </c>
       <c r="B5" t="n">
-        <v>91001</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,38 +1059,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598355</v>
+        <v>598312</v>
       </c>
       <c r="R5" t="n">
-        <v>6922329</v>
+        <v>6922247</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1121,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1127,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1161,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Erik Lagerin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1168,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123304268</v>
+        <v>123304259</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,38 +1188,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598312</v>
+        <v>598360</v>
       </c>
       <c r="R6" t="n">
-        <v>6922247</v>
+        <v>6922325</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Erik Lagerin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 29694-2024 artfynd.xlsx
+++ b/artfynd/A 29694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123304265</v>
+        <v>123304268</v>
       </c>
       <c r="B2" t="n">
-        <v>91277</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598319</v>
+        <v>598312</v>
       </c>
       <c r="R2" t="n">
-        <v>6922248</v>
+        <v>6922247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -785,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Lagerin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Erik Lagerin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -796,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123304257</v>
+        <v>123304264</v>
       </c>
       <c r="B3" t="n">
         <v>91001</v>
@@ -829,26 +833,17 @@
           <t>Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598358</v>
+        <v>598355</v>
       </c>
       <c r="R3" t="n">
-        <v>6922402</v>
+        <v>6922329</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +870,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -885,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +910,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Erik Lagerin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -926,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123304264</v>
+        <v>123304265</v>
       </c>
       <c r="B4" t="n">
-        <v>91001</v>
+        <v>91277</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,25 +933,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598355</v>
+        <v>598319</v>
       </c>
       <c r="R4" t="n">
-        <v>6922329</v>
+        <v>6922248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1006,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123304268</v>
+        <v>123304257</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>91001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,30 +1054,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598312</v>
+        <v>598358</v>
       </c>
       <c r="R5" t="n">
-        <v>6922247</v>
+        <v>6922402</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Erik Lagerin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
